--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -1,121 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="HitPlanHit" sheetId="1" r:id="rId1"/>
+    <sheet name="HitPlanHit" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>HitPlanHit</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>df0d9f01c3e44551</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>hit_plan_id</t>
-  </si>
-  <si>
-    <t>sequence</t>
-  </si>
-  <si>
-    <t>target_group</t>
-  </si>
-  <si>
-    <t>damage_ratio_decimal</t>
-  </si>
-  <si>
-    <t>toughness_ratio_decimal</t>
-  </si>
-  <si>
-    <t>crit_policy</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;HitPlan.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>enum&lt;HitTargetGroup&gt;</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>enum&lt;CritPolicy&gt;</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>range=1..100</t>
-  </si>
-  <si>
-    <t>length=1..32</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -134,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -428,148 +407,1412 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>27</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>HitPlanHit</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>df0d9f01c3e44551</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>hit_plan_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>damage_ratio_decimal</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>toughness_ratio_decimal</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>crit_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hit_plan_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>damage_ratio_decimal</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>toughness_ratio_decimal</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>crit_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;HitPlan.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>enum&lt;HitTargetGroup&gt;</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>enum&lt;CritPolicy&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>range=1..100</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>length=1..32</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>length=1..32</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>12001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>12003</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>12004</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>12006</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>12007</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>12008</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>12009</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>12012</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>12013</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>12014</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>12017</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>12018</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>12019</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>12021</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>12023</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>12024</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>12025</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>12027</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>12029</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>12030</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>12031</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>12032</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>12036</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>12037</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>12038</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>12040</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>12041</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>12042</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>12044</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>12045</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>12047</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>12048</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>12049</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>12052</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>12053</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>12055</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>12057</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>12058</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>12059</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>12060</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>12062</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>12063</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1815,6 +1815,1210 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>21001</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>21002</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>21003</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.666666</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.666666</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>21003</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>21004</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>21005</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>21005</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>21005</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>21005</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>21005</v>
+      </c>
+      <c r="C59" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>21006</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>21007</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>21008</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>21008</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>21009</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>21010</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>21011</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>21012</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>21013</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>21014</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0.666666</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0.666666</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>21014</v>
+      </c>
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>21015</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>21016</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>21017</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>21018</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>21019</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0.666666</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0.666666</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>21019</v>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>21020</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>21021</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>21022</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>21023</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>21025</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>21026</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>21026</v>
+      </c>
+      <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>21026</v>
+      </c>
+      <c r="C86" t="n">
+        <v>3</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>21026</v>
+      </c>
+      <c r="C87" t="n">
+        <v>4</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>21026</v>
+      </c>
+      <c r="C88" t="n">
+        <v>5</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>21027</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>21028</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>21029</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>21030</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,16 +24,68 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,12 +93,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,237 +499,340 @@
   </sheetPr>
   <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="15.7109375" customWidth="1" style="5" min="2" max="2"/>
+    <col width="12.7109375" customWidth="1" style="5" min="3" max="3"/>
+    <col width="20.7109375" customWidth="1" style="5" min="4" max="5"/>
+    <col width="23.7109375" customWidth="1" style="5" min="6" max="6"/>
+    <col width="16.7109375" customWidth="1" style="5" min="7" max="7"/>
+    <col width="29.7109375" customWidth="1" style="5" min="8" max="8"/>
+    <col width="30.7109375" customWidth="1" style="5" min="9" max="9"/>
+    <col width="24.7109375" customWidth="1" style="5" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>@table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>HitPlanHit</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>@mode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>@key</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>@scope</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>@schema</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>df0d9f01c3e44551</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>ba104ad9faac7ac3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>#name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>hit_plan_id</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>sequence</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>target_group</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>damage_ratio_decimal</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>toughness_ratio_decimal</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>crit_policy</t>
         </is>
       </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>damage_parameter_key_override</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>damage_operation_ratio_decimal</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>toughness_amount_decimal</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>#field</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>hit_plan_id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>sequence</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>target_group</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>damage_ratio_decimal</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>toughness_ratio_decimal</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>crit_policy</t>
         </is>
       </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>damage_parameter_key_override</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>damage_operation_ratio_decimal</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>toughness_amount_decimal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>#type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>ref&lt;HitPlan.id&gt;</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>i32</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>enum&lt;HitTargetGroup&gt;</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>enum&lt;CritPolicy&gt;</t>
         </is>
       </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>optional&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>optional&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>optional&lt;string&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>#scope</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>#input</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>range=1..100</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>length=1..32</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>length=1..32</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>length=1..120</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>length=1..32</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>length=1..32</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" t="n">
-        <v>12001</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12001</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -668,11 +856,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>12003</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12003</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -696,11 +888,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>12004</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12004</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -724,11 +920,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>12006</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12006</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -752,11 +952,15 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>12007</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12007</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -780,11 +984,15 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>12008</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12008</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -808,11 +1016,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>12009</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12009</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -836,11 +1048,15 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>12012</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12012</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -864,11 +1080,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>12013</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12013</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -892,11 +1112,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>12014</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12014</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -920,11 +1144,15 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
-        <v>12017</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12017</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -948,11 +1176,15 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
-        <v>12018</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12018</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -976,11 +1208,15 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
-        <v>12019</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12019</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1004,11 +1240,15 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
-        <v>12021</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12021</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1032,11 +1272,15 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
-        <v>12023</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12023</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1060,11 +1304,15 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>12024</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>12024</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1088,11 +1336,15 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
-        <v>12025</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12025</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1116,11 +1368,15 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
-        <v>12027</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>12027</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1144,11 +1400,15 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
-        <v>12029</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12029</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1172,11 +1432,15 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
-        <v>12030</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12030</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1200,11 +1464,15 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
-        <v>12031</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12031</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1228,11 +1496,15 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
-        <v>12032</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>12032</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1256,11 +1528,15 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
-        <v>12036</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>12036</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1284,11 +1560,15 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
-        <v>12037</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>12037</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1312,11 +1592,15 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="n">
-        <v>12038</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>12038</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1340,11 +1624,15 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
-        <v>12040</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>12040</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1368,11 +1656,15 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
-        <v>12041</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>12041</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1396,11 +1688,15 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
-        <v>12042</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>12042</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1424,11 +1720,15 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
-        <v>12044</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>12044</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1452,11 +1752,15 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="n">
-        <v>12045</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>12045</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1480,11 +1784,15 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="n">
-        <v>12047</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>12047</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1508,11 +1816,15 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="n">
-        <v>12048</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1536,11 +1848,15 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="n">
-        <v>12049</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>12049</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1564,11 +1880,15 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="n">
-        <v>12052</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>12052</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1592,11 +1912,15 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="n">
-        <v>12053</v>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>12053</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1620,11 +1944,15 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="n">
-        <v>12055</v>
-      </c>
-      <c r="C43" t="n">
-        <v>1</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>12055</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1648,11 +1976,15 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="n">
-        <v>12057</v>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>12057</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1676,11 +2008,15 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="n">
-        <v>12058</v>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>12058</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1704,11 +2040,15 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="n">
-        <v>12059</v>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>12059</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1732,11 +2072,15 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="n">
-        <v>12060</v>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>12060</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1760,11 +2104,15 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="n">
-        <v>12062</v>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>12062</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1788,11 +2136,15 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="n">
-        <v>12063</v>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>12063</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1982,6 +2334,16 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
@@ -2010,6 +2372,16 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
@@ -2038,6 +2410,16 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
@@ -2066,6 +2448,16 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
@@ -2094,6 +2486,16 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
@@ -2542,6 +2944,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
@@ -2570,6 +2987,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
@@ -3020,6 +3452,18 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">
+      <formula1>1</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Primary, Adjacent, Selected, All, BounceDraw, SelfTarget" promptTitle="HitTargetGroup enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"Primary,Adjacent,Selected,All,BounceDraw,SelfTarget"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: PerTarget, Shared, Never" promptTitle="CritPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"PerTarget,Shared,Never"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2250,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
@@ -2278,6 +2293,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
@@ -2306,6 +2336,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
@@ -2334,6 +2379,11 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>1</t>
@@ -2372,6 +2422,11 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>1</t>
@@ -2410,6 +2465,11 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>1</t>
@@ -2448,6 +2508,11 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>1</t>
@@ -2486,6 +2551,11 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>1</t>
@@ -2552,6 +2622,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
@@ -2580,6 +2665,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
@@ -2608,6 +2708,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
@@ -2636,6 +2751,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
@@ -2692,6 +2822,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
@@ -2776,6 +2921,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
@@ -2804,6 +2964,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
@@ -2832,6 +3007,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
@@ -2860,6 +3050,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
@@ -2888,6 +3093,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
@@ -3030,6 +3250,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
@@ -3086,6 +3321,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
@@ -3114,6 +3364,21 @@
           <t>PerTarget</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
@@ -3129,17 +3394,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3148,91 +3428,136 @@
         <v>21024</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>BounceDraw</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>21025</v>
+        <v>21024</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>BounceDraw</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>21026</v>
+        <v>21024</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>BounceDraw</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>21026</v>
+        <v>21024</v>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -3241,26 +3566,41 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>21026</v>
+        <v>21024</v>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3269,26 +3609,41 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>21026</v>
+        <v>21024</v>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3297,26 +3652,41 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>21026</v>
+        <v>21024</v>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3325,129 +3695,4109 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>21027</v>
+        <v>21024</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>BounceDraw</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>21028</v>
+        <v>21024</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>BounceDraw</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>21029</v>
+        <v>21024</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>BounceDraw</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.029411</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C93" t="n">
+        <v>20</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C94" t="n">
+        <v>21</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C95" t="n">
+        <v>22</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C96" t="n">
+        <v>23</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C97" t="n">
+        <v>24</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C98" t="n">
+        <v>25</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C99" t="n">
+        <v>26</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C100" t="n">
+        <v>27</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C101" t="n">
+        <v>28</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C102" t="n">
+        <v>29</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C104" t="n">
+        <v>30</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C105" t="n">
+        <v>31</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C106" t="n">
+        <v>32</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C107" t="n">
+        <v>33</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C108" t="n">
+        <v>34</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0.029437</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>0.029437</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C109" t="n">
+        <v>4</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C110" t="n">
+        <v>5</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C111" t="n">
+        <v>6</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C112" t="n">
+        <v>7</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C113" t="n">
+        <v>8</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>21024</v>
+      </c>
+      <c r="C114" t="n">
+        <v>9</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>21025</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>21026</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>21026</v>
+      </c>
+      <c r="C117" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>21026</v>
+      </c>
+      <c r="C118" t="n">
+        <v>3</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>21026</v>
+      </c>
+      <c r="C119" t="n">
+        <v>4</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>21026</v>
+      </c>
+      <c r="C120" t="n">
+        <v>5</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>21026</v>
+      </c>
+      <c r="C121" t="n">
+        <v>6</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>0.16667</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0.16667</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>21027</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>21028</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>21029</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
         <v>21030</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C125" t="n">
         <v>1</v>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>PerTarget</t>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C127" t="n">
+        <v>10</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C128" t="n">
+        <v>11</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C129" t="n">
+        <v>12</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C130" t="n">
+        <v>13</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C131" t="n">
+        <v>14</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C132" t="n">
+        <v>15</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C133" t="n">
+        <v>16</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C134" t="n">
+        <v>17</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C135" t="n">
+        <v>18</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C136" t="n">
+        <v>19</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C137" t="n">
+        <v>2</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C138" t="n">
+        <v>20</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C139" t="n">
+        <v>21</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C140" t="n">
+        <v>22</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C141" t="n">
+        <v>23</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C142" t="n">
+        <v>24</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C143" t="n">
+        <v>25</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C144" t="n">
+        <v>26</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C145" t="n">
+        <v>27</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C146" t="n">
+        <v>28</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C147" t="n">
+        <v>29</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C148" t="n">
+        <v>3</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C149" t="n">
+        <v>30</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C150" t="n">
+        <v>31</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C151" t="n">
+        <v>32</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C152" t="n">
+        <v>33</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C153" t="n">
+        <v>34</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0.029437</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>0.029437</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C154" t="n">
+        <v>4</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C155" t="n">
+        <v>5</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C156" t="n">
+        <v>6</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C157" t="n">
+        <v>7</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C158" t="n">
+        <v>8</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>21990</v>
+      </c>
+      <c r="C159" t="n">
+        <v>9</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>0.029411</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C161" t="n">
+        <v>10</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C162" t="n">
+        <v>11</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C163" t="n">
+        <v>12</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C164" t="n">
+        <v>13</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C165" t="n">
+        <v>14</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C166" t="n">
+        <v>15</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C167" t="n">
+        <v>16</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C168" t="n">
+        <v>17</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C169" t="n">
+        <v>18</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C170" t="n">
+        <v>19</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C171" t="n">
+        <v>2</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C172" t="n">
+        <v>20</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C173" t="n">
+        <v>21</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C174" t="n">
+        <v>22</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C175" t="n">
+        <v>23</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C176" t="n">
+        <v>24</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C177" t="n">
+        <v>25</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C178" t="n">
+        <v>26</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C179" t="n">
+        <v>27</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C180" t="n">
+        <v>28</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C181" t="n">
+        <v>29</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C182" t="n">
+        <v>3</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C183" t="n">
+        <v>30</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C184" t="n">
+        <v>31</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C185" t="n">
+        <v>32</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C186" t="n">
+        <v>4</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C187" t="n">
+        <v>5</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C188" t="n">
+        <v>6</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C189" t="n">
+        <v>7</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C190" t="n">
+        <v>8</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>21991</v>
+      </c>
+      <c r="C191" t="n">
+        <v>9</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>0.03125</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>21992</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>

--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J192"/>
+  <dimension ref="A1:J250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -7796,6 +7796,2425 @@
         </is>
       </c>
       <c r="J192" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>31001</v>
+      </c>
+      <c r="C193" t="n">
+        <v>1</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>31001</v>
+      </c>
+      <c r="C194" t="n">
+        <v>2</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>31002</v>
+      </c>
+      <c r="C195" t="n">
+        <v>1</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>31003</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>31003</v>
+      </c>
+      <c r="C197" t="n">
+        <v>2</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>31004</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>parameter.06</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>31004</v>
+      </c>
+      <c r="C199" t="n">
+        <v>2</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>parameter.07</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>31005</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>31006</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>31007</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>31007</v>
+      </c>
+      <c r="C203" t="n">
+        <v>2</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>31007</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>31007</v>
+      </c>
+      <c r="C205" t="n">
+        <v>4</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>31007</v>
+      </c>
+      <c r="C206" t="n">
+        <v>5</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>31008</v>
+      </c>
+      <c r="C207" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>31009</v>
+      </c>
+      <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>31010</v>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>31010</v>
+      </c>
+      <c r="C210" t="n">
+        <v>2</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>31010</v>
+      </c>
+      <c r="C211" t="n">
+        <v>3</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>31010</v>
+      </c>
+      <c r="C212" t="n">
+        <v>4</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>31010</v>
+      </c>
+      <c r="C213" t="n">
+        <v>5</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>31011</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>31011</v>
+      </c>
+      <c r="C215" t="n">
+        <v>2</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>31012</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>31013</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>31014</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>31015</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>31016</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>31017</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>31018</v>
+      </c>
+      <c r="C222" t="n">
+        <v>1</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>31019</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>31020</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>31020</v>
+      </c>
+      <c r="C225" t="n">
+        <v>2</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>31020</v>
+      </c>
+      <c r="C226" t="n">
+        <v>3</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>31020</v>
+      </c>
+      <c r="C227" t="n">
+        <v>4</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>31020</v>
+      </c>
+      <c r="C228" t="n">
+        <v>5</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>31020</v>
+      </c>
+      <c r="C229" t="n">
+        <v>6</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>31020</v>
+      </c>
+      <c r="C230" t="n">
+        <v>7</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>0.142858</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>0.142858</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>31021</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>31021</v>
+      </c>
+      <c r="C232" t="n">
+        <v>2</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>31022</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>31023</v>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>31024</v>
+      </c>
+      <c r="C235" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>31025</v>
+      </c>
+      <c r="C236" t="n">
+        <v>1</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>31026</v>
+      </c>
+      <c r="C237" t="n">
+        <v>1</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>31027</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>31028</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>31029</v>
+      </c>
+      <c r="C240" t="n">
+        <v>1</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>31030</v>
+      </c>
+      <c r="C241" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>31031</v>
+      </c>
+      <c r="C242" t="n">
+        <v>1</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>31031</v>
+      </c>
+      <c r="C243" t="n">
+        <v>2</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>31031</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>31031</v>
+      </c>
+      <c r="C245" t="n">
+        <v>4</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>31031</v>
+      </c>
+      <c r="C246" t="n">
+        <v>5</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>31031</v>
+      </c>
+      <c r="C247" t="n">
+        <v>6</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>0.142857</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>31031</v>
+      </c>
+      <c r="C248" t="n">
+        <v>7</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>0.142858</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>0.142858</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>31032</v>
+      </c>
+      <c r="C249" t="n">
+        <v>1</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>31033</v>
+      </c>
+      <c r="C250" t="n">
+        <v>1</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
         <is>
           <t>30</t>
         </is>

--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J250"/>
+  <dimension ref="A1:J280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -10217,6 +10217,1296 @@
       <c r="J250" t="inlineStr">
         <is>
           <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>41001</v>
+      </c>
+      <c r="C251" t="n">
+        <v>1</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>41002</v>
+      </c>
+      <c r="C252" t="n">
+        <v>1</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>41002</v>
+      </c>
+      <c r="C253" t="n">
+        <v>2</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>41003</v>
+      </c>
+      <c r="C254" t="n">
+        <v>1</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>41004</v>
+      </c>
+      <c r="C255" t="n">
+        <v>1</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>41004</v>
+      </c>
+      <c r="C256" t="n">
+        <v>2</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>41005</v>
+      </c>
+      <c r="C257" t="n">
+        <v>1</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>41005</v>
+      </c>
+      <c r="C258" t="n">
+        <v>2</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>parameter.05</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>41006</v>
+      </c>
+      <c r="C259" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>41007</v>
+      </c>
+      <c r="C260" t="n">
+        <v>1</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>41008</v>
+      </c>
+      <c r="C261" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>41009</v>
+      </c>
+      <c r="C262" t="n">
+        <v>1</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>41010</v>
+      </c>
+      <c r="C263" t="n">
+        <v>1</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>41011</v>
+      </c>
+      <c r="C264" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>41012</v>
+      </c>
+      <c r="C265" t="n">
+        <v>1</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>41013</v>
+      </c>
+      <c r="C266" t="n">
+        <v>1</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>41014</v>
+      </c>
+      <c r="C267" t="n">
+        <v>1</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>41015</v>
+      </c>
+      <c r="C268" t="n">
+        <v>1</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>41015</v>
+      </c>
+      <c r="C269" t="n">
+        <v>2</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>41016</v>
+      </c>
+      <c r="C270" t="n">
+        <v>1</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>41017</v>
+      </c>
+      <c r="C271" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>41018</v>
+      </c>
+      <c r="C272" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>41018</v>
+      </c>
+      <c r="C273" t="n">
+        <v>2</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>41019</v>
+      </c>
+      <c r="C274" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>41020</v>
+      </c>
+      <c r="C275" t="n">
+        <v>1</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>41021</v>
+      </c>
+      <c r="C276" t="n">
+        <v>1</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>41021</v>
+      </c>
+      <c r="C277" t="n">
+        <v>2</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>41022</v>
+      </c>
+      <c r="C278" t="n">
+        <v>1</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>41023</v>
+      </c>
+      <c r="C279" t="n">
+        <v>1</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>41023</v>
+      </c>
+      <c r="C280" t="n">
+        <v>2</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>

--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J280"/>
+  <dimension ref="A1:J315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -11507,6 +11507,1501 @@
       <c r="J280" t="inlineStr">
         <is>
           <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>51001</v>
+      </c>
+      <c r="C281" t="n">
+        <v>1</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>51001</v>
+      </c>
+      <c r="C282" t="n">
+        <v>2</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>51002</v>
+      </c>
+      <c r="C283" t="n">
+        <v>1</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>51003</v>
+      </c>
+      <c r="C284" t="n">
+        <v>1</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>51003</v>
+      </c>
+      <c r="C285" t="n">
+        <v>2</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>51004</v>
+      </c>
+      <c r="C286" t="n">
+        <v>1</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>51004</v>
+      </c>
+      <c r="C287" t="n">
+        <v>2</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>51005</v>
+      </c>
+      <c r="C288" t="n">
+        <v>1</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>51006</v>
+      </c>
+      <c r="C289" t="n">
+        <v>1</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>51007</v>
+      </c>
+      <c r="C290" t="n">
+        <v>1</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>51008</v>
+      </c>
+      <c r="C291" t="n">
+        <v>1</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>51009</v>
+      </c>
+      <c r="C292" t="n">
+        <v>1</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>51010</v>
+      </c>
+      <c r="C293" t="n">
+        <v>1</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>51011</v>
+      </c>
+      <c r="C294" t="n">
+        <v>1</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>51012</v>
+      </c>
+      <c r="C295" t="n">
+        <v>1</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>51013</v>
+      </c>
+      <c r="C296" t="n">
+        <v>1</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>51014</v>
+      </c>
+      <c r="C297" t="n">
+        <v>1</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>51015</v>
+      </c>
+      <c r="C298" t="n">
+        <v>1</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>51016</v>
+      </c>
+      <c r="C299" t="n">
+        <v>1</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>51016</v>
+      </c>
+      <c r="C300" t="n">
+        <v>2</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>51017</v>
+      </c>
+      <c r="C301" t="n">
+        <v>1</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>51018</v>
+      </c>
+      <c r="C302" t="n">
+        <v>1</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>51019</v>
+      </c>
+      <c r="C303" t="n">
+        <v>1</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>51020</v>
+      </c>
+      <c r="C304" t="n">
+        <v>1</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>51021</v>
+      </c>
+      <c r="C305" t="n">
+        <v>1</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>51022</v>
+      </c>
+      <c r="C306" t="n">
+        <v>1</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>51023</v>
+      </c>
+      <c r="C307" t="n">
+        <v>1</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>51024</v>
+      </c>
+      <c r="C308" t="n">
+        <v>1</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>51025</v>
+      </c>
+      <c r="C309" t="n">
+        <v>1</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>51026</v>
+      </c>
+      <c r="C310" t="n">
+        <v>1</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>51027</v>
+      </c>
+      <c r="C311" t="n">
+        <v>1</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>51028</v>
+      </c>
+      <c r="C312" t="n">
+        <v>1</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>51029</v>
+      </c>
+      <c r="C313" t="n">
+        <v>1</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>51030</v>
+      </c>
+      <c r="C314" t="n">
+        <v>1</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>51031</v>
+      </c>
+      <c r="C315" t="n">
+        <v>1</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
     </row>

--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K368"/>
+  <dimension ref="A1:K398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -16389,6 +16389,1291 @@
       <c r="J368" t="inlineStr">
         <is>
           <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="n">
+        <v>71001</v>
+      </c>
+      <c r="C369" t="n">
+        <v>1</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="n">
+        <v>71002</v>
+      </c>
+      <c r="C370" t="n">
+        <v>1</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="n">
+        <v>71002</v>
+      </c>
+      <c r="C371" t="n">
+        <v>2</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" t="n">
+        <v>71003</v>
+      </c>
+      <c r="C372" t="n">
+        <v>1</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="n">
+        <v>71004</v>
+      </c>
+      <c r="C373" t="n">
+        <v>1</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" t="n">
+        <v>71005</v>
+      </c>
+      <c r="C374" t="n">
+        <v>1</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="n">
+        <v>71006</v>
+      </c>
+      <c r="C375" t="n">
+        <v>1</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="n">
+        <v>71007</v>
+      </c>
+      <c r="C376" t="n">
+        <v>1</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="n">
+        <v>71008</v>
+      </c>
+      <c r="C377" t="n">
+        <v>1</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="n">
+        <v>71009</v>
+      </c>
+      <c r="C378" t="n">
+        <v>1</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="n">
+        <v>71010</v>
+      </c>
+      <c r="C379" t="n">
+        <v>1</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>parameter.05</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="n">
+        <v>71011</v>
+      </c>
+      <c r="C380" t="n">
+        <v>1</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" t="n">
+        <v>71011</v>
+      </c>
+      <c r="C381" t="n">
+        <v>2</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="n">
+        <v>71012</v>
+      </c>
+      <c r="C382" t="n">
+        <v>1</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" t="n">
+        <v>71013</v>
+      </c>
+      <c r="C383" t="n">
+        <v>1</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="n">
+        <v>71014</v>
+      </c>
+      <c r="C384" t="n">
+        <v>1</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" t="n">
+        <v>71015</v>
+      </c>
+      <c r="C385" t="n">
+        <v>1</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" t="n">
+        <v>71015</v>
+      </c>
+      <c r="C386" t="n">
+        <v>2</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" t="n">
+        <v>71016</v>
+      </c>
+      <c r="C387" t="n">
+        <v>1</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" t="n">
+        <v>71017</v>
+      </c>
+      <c r="C388" t="n">
+        <v>1</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" t="n">
+        <v>71018</v>
+      </c>
+      <c r="C389" t="n">
+        <v>1</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" t="n">
+        <v>71018</v>
+      </c>
+      <c r="C390" t="n">
+        <v>2</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" t="n">
+        <v>71018</v>
+      </c>
+      <c r="C391" t="n">
+        <v>3</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" t="n">
+        <v>71019</v>
+      </c>
+      <c r="C392" t="n">
+        <v>1</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" t="n">
+        <v>71020</v>
+      </c>
+      <c r="C393" t="n">
+        <v>1</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" t="n">
+        <v>71020</v>
+      </c>
+      <c r="C394" t="n">
+        <v>2</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" t="n">
+        <v>71021</v>
+      </c>
+      <c r="C395" t="n">
+        <v>1</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" t="n">
+        <v>71022</v>
+      </c>
+      <c r="C396" t="n">
+        <v>1</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" t="n">
+        <v>71022</v>
+      </c>
+      <c r="C397" t="n">
+        <v>2</v>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" t="n">
+        <v>71023</v>
+      </c>
+      <c r="C398" t="n">
+        <v>1</v>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
     </row>

--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K398"/>
+  <dimension ref="A1:K436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -17672,6 +17672,1635 @@
         </is>
       </c>
       <c r="J398" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" t="n">
+        <v>81001</v>
+      </c>
+      <c r="C399" t="n">
+        <v>1</v>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" t="n">
+        <v>81002</v>
+      </c>
+      <c r="C400" t="n">
+        <v>1</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" t="n">
+        <v>81002</v>
+      </c>
+      <c r="C401" t="n">
+        <v>2</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>parameter.08</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" t="n">
+        <v>81003</v>
+      </c>
+      <c r="C402" t="n">
+        <v>1</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" t="n">
+        <v>81004</v>
+      </c>
+      <c r="C403" t="n">
+        <v>1</v>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" t="n">
+        <v>81005</v>
+      </c>
+      <c r="C404" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" t="n">
+        <v>81006</v>
+      </c>
+      <c r="C405" t="n">
+        <v>1</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" t="n">
+        <v>81007</v>
+      </c>
+      <c r="C406" t="n">
+        <v>1</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" t="n">
+        <v>81008</v>
+      </c>
+      <c r="C407" t="n">
+        <v>1</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" t="n">
+        <v>81009</v>
+      </c>
+      <c r="C408" t="n">
+        <v>1</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" t="n">
+        <v>81009</v>
+      </c>
+      <c r="C409" t="n">
+        <v>2</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" t="n">
+        <v>81009</v>
+      </c>
+      <c r="C410" t="n">
+        <v>3</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" t="n">
+        <v>81009</v>
+      </c>
+      <c r="C411" t="n">
+        <v>4</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" t="n">
+        <v>81010</v>
+      </c>
+      <c r="C412" t="n">
+        <v>1</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" t="n">
+        <v>81011</v>
+      </c>
+      <c r="C413" t="n">
+        <v>1</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" t="n">
+        <v>81012</v>
+      </c>
+      <c r="C414" t="n">
+        <v>1</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" t="n">
+        <v>81013</v>
+      </c>
+      <c r="C415" t="n">
+        <v>1</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" t="n">
+        <v>81014</v>
+      </c>
+      <c r="C416" t="n">
+        <v>1</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" t="n">
+        <v>81015</v>
+      </c>
+      <c r="C417" t="n">
+        <v>1</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" t="n">
+        <v>81016</v>
+      </c>
+      <c r="C418" t="n">
+        <v>1</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" t="n">
+        <v>81016</v>
+      </c>
+      <c r="C419" t="n">
+        <v>2</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" t="n">
+        <v>81016</v>
+      </c>
+      <c r="C420" t="n">
+        <v>3</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" t="n">
+        <v>81017</v>
+      </c>
+      <c r="C421" t="n">
+        <v>1</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" t="n">
+        <v>81018</v>
+      </c>
+      <c r="C422" t="n">
+        <v>1</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" t="n">
+        <v>81019</v>
+      </c>
+      <c r="C423" t="n">
+        <v>1</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" t="n">
+        <v>81020</v>
+      </c>
+      <c r="C424" t="n">
+        <v>1</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" t="n">
+        <v>81020</v>
+      </c>
+      <c r="C425" t="n">
+        <v>2</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" t="n">
+        <v>81020</v>
+      </c>
+      <c r="C426" t="n">
+        <v>3</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" t="n">
+        <v>81021</v>
+      </c>
+      <c r="C427" t="n">
+        <v>1</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" t="n">
+        <v>81021</v>
+      </c>
+      <c r="C428" t="n">
+        <v>2</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" t="n">
+        <v>81022</v>
+      </c>
+      <c r="C429" t="n">
+        <v>1</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" t="n">
+        <v>81023</v>
+      </c>
+      <c r="C430" t="n">
+        <v>1</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" t="n">
+        <v>81023</v>
+      </c>
+      <c r="C431" t="n">
+        <v>2</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" t="n">
+        <v>81023</v>
+      </c>
+      <c r="C432" t="n">
+        <v>3</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" t="n">
+        <v>81023</v>
+      </c>
+      <c r="C433" t="n">
+        <v>4</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" t="n">
+        <v>81023</v>
+      </c>
+      <c r="C434" t="n">
+        <v>5</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" t="n">
+        <v>81024</v>
+      </c>
+      <c r="C435" t="n">
+        <v>1</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" t="n">
+        <v>81025</v>
+      </c>
+      <c r="C436" t="n">
+        <v>1</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
         <is>
           <t>60</t>
         </is>

--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K436"/>
+  <dimension ref="A1:K497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -19303,6 +19303,2624 @@
       <c r="J436" t="inlineStr">
         <is>
           <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" t="n">
+        <v>91001</v>
+      </c>
+      <c r="C437" t="n">
+        <v>1</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" t="n">
+        <v>91002</v>
+      </c>
+      <c r="C438" t="n">
+        <v>1</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" t="n">
+        <v>91003</v>
+      </c>
+      <c r="C439" t="n">
+        <v>1</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" t="n">
+        <v>91004</v>
+      </c>
+      <c r="C440" t="n">
+        <v>1</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="B441" t="n">
+        <v>91005</v>
+      </c>
+      <c r="C441" t="n">
+        <v>1</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" t="n">
+        <v>91006</v>
+      </c>
+      <c r="C442" t="n">
+        <v>1</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" t="n">
+        <v>91006</v>
+      </c>
+      <c r="C443" t="n">
+        <v>2</v>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="B444" t="n">
+        <v>91007</v>
+      </c>
+      <c r="C444" t="n">
+        <v>1</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="B445" t="n">
+        <v>91007</v>
+      </c>
+      <c r="C445" t="n">
+        <v>2</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="B446" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C446" t="n">
+        <v>1</v>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="B447" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C447" t="n">
+        <v>2</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="B448" t="n">
+        <v>91009</v>
+      </c>
+      <c r="C448" t="n">
+        <v>1</v>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="B449" t="n">
+        <v>91009</v>
+      </c>
+      <c r="C449" t="n">
+        <v>2</v>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="B450" t="n">
+        <v>91010</v>
+      </c>
+      <c r="C450" t="n">
+        <v>1</v>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="B451" t="n">
+        <v>91011</v>
+      </c>
+      <c r="C451" t="n">
+        <v>1</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="B452" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C452" t="n">
+        <v>1</v>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="B453" t="n">
+        <v>91013</v>
+      </c>
+      <c r="C453" t="n">
+        <v>1</v>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="B454" t="n">
+        <v>91014</v>
+      </c>
+      <c r="C454" t="n">
+        <v>1</v>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="B455" t="n">
+        <v>91015</v>
+      </c>
+      <c r="C455" t="n">
+        <v>1</v>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="B456" t="n">
+        <v>91016</v>
+      </c>
+      <c r="C456" t="n">
+        <v>1</v>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="B457" t="n">
+        <v>91017</v>
+      </c>
+      <c r="C457" t="n">
+        <v>1</v>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" t="n">
+        <v>91018</v>
+      </c>
+      <c r="C458" t="n">
+        <v>1</v>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" t="n">
+        <v>91018</v>
+      </c>
+      <c r="C459" t="n">
+        <v>2</v>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="B460" t="n">
+        <v>91018</v>
+      </c>
+      <c r="C460" t="n">
+        <v>3</v>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="B461" t="n">
+        <v>91018</v>
+      </c>
+      <c r="C461" t="n">
+        <v>4</v>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="B462" t="n">
+        <v>91018</v>
+      </c>
+      <c r="C462" t="n">
+        <v>5</v>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="B463" t="n">
+        <v>91019</v>
+      </c>
+      <c r="C463" t="n">
+        <v>1</v>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="B464" t="n">
+        <v>91019</v>
+      </c>
+      <c r="C464" t="n">
+        <v>2</v>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="B465" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C465" t="n">
+        <v>1</v>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="B466" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C466" t="n">
+        <v>10</v>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="B467" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C467" t="n">
+        <v>11</v>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="B468" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C468" t="n">
+        <v>12</v>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="B469" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C469" t="n">
+        <v>13</v>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="B470" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C470" t="n">
+        <v>14</v>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="B471" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C471" t="n">
+        <v>15</v>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="B472" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C472" t="n">
+        <v>16</v>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="B473" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C473" t="n">
+        <v>17</v>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>0.058832</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>0.058832</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="B474" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C474" t="n">
+        <v>2</v>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="B475" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C475" t="n">
+        <v>3</v>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="B476" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C476" t="n">
+        <v>4</v>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="B477" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C477" t="n">
+        <v>5</v>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="B478" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C478" t="n">
+        <v>6</v>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="B479" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C479" t="n">
+        <v>7</v>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="B480" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C480" t="n">
+        <v>8</v>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="B481" t="n">
+        <v>91020</v>
+      </c>
+      <c r="C481" t="n">
+        <v>9</v>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>0.058823</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="B482" t="n">
+        <v>91021</v>
+      </c>
+      <c r="C482" t="n">
+        <v>1</v>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="B483" t="n">
+        <v>91022</v>
+      </c>
+      <c r="C483" t="n">
+        <v>1</v>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="B484" t="n">
+        <v>91022</v>
+      </c>
+      <c r="C484" t="n">
+        <v>2</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="B485" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C485" t="n">
+        <v>1</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="B486" t="n">
+        <v>91024</v>
+      </c>
+      <c r="C486" t="n">
+        <v>1</v>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="B487" t="n">
+        <v>91025</v>
+      </c>
+      <c r="C487" t="n">
+        <v>1</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="B488" t="n">
+        <v>91025</v>
+      </c>
+      <c r="C488" t="n">
+        <v>2</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="B489" t="n">
+        <v>91026</v>
+      </c>
+      <c r="C489" t="n">
+        <v>1</v>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="B490" t="n">
+        <v>91027</v>
+      </c>
+      <c r="C490" t="n">
+        <v>1</v>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="B491" t="n">
+        <v>91027</v>
+      </c>
+      <c r="C491" t="n">
+        <v>2</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="B492" t="n">
+        <v>91027</v>
+      </c>
+      <c r="C492" t="n">
+        <v>3</v>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="B493" t="n">
+        <v>91027</v>
+      </c>
+      <c r="C493" t="n">
+        <v>4</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="B494" t="n">
+        <v>91027</v>
+      </c>
+      <c r="C494" t="n">
+        <v>5</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="B495" t="n">
+        <v>91028</v>
+      </c>
+      <c r="C495" t="n">
+        <v>1</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="B496" t="n">
+        <v>91029</v>
+      </c>
+      <c r="C496" t="n">
+        <v>1</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="B497" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C497" t="n">
+        <v>1</v>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>

--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K497"/>
+  <dimension ref="A1:K560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -21921,6 +21921,2633 @@
       <c r="J497" t="inlineStr">
         <is>
           <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="B498" t="n">
+        <v>101001</v>
+      </c>
+      <c r="C498" t="n">
+        <v>1</v>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="B499" t="n">
+        <v>101002</v>
+      </c>
+      <c r="C499" t="n">
+        <v>1</v>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="B500" t="n">
+        <v>101002</v>
+      </c>
+      <c r="C500" t="n">
+        <v>10</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="B501" t="n">
+        <v>101002</v>
+      </c>
+      <c r="C501" t="n">
+        <v>11</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>0.09091</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>0.09091</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="B502" t="n">
+        <v>101002</v>
+      </c>
+      <c r="C502" t="n">
+        <v>2</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="B503" t="n">
+        <v>101002</v>
+      </c>
+      <c r="C503" t="n">
+        <v>3</v>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="B504" t="n">
+        <v>101002</v>
+      </c>
+      <c r="C504" t="n">
+        <v>4</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="B505" t="n">
+        <v>101002</v>
+      </c>
+      <c r="C505" t="n">
+        <v>5</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="B506" t="n">
+        <v>101002</v>
+      </c>
+      <c r="C506" t="n">
+        <v>6</v>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="B507" t="n">
+        <v>101002</v>
+      </c>
+      <c r="C507" t="n">
+        <v>7</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="B508" t="n">
+        <v>101002</v>
+      </c>
+      <c r="C508" t="n">
+        <v>8</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="B509" t="n">
+        <v>101002</v>
+      </c>
+      <c r="C509" t="n">
+        <v>9</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>0.090909</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="B510" t="n">
+        <v>101003</v>
+      </c>
+      <c r="C510" t="n">
+        <v>1</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="B511" t="n">
+        <v>101004</v>
+      </c>
+      <c r="C511" t="n">
+        <v>1</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="B512" t="n">
+        <v>101005</v>
+      </c>
+      <c r="C512" t="n">
+        <v>1</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="B513" t="n">
+        <v>101005</v>
+      </c>
+      <c r="C513" t="n">
+        <v>2</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="B514" t="n">
+        <v>101006</v>
+      </c>
+      <c r="C514" t="n">
+        <v>1</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="B515" t="n">
+        <v>101007</v>
+      </c>
+      <c r="C515" t="n">
+        <v>1</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="B516" t="n">
+        <v>101007</v>
+      </c>
+      <c r="C516" t="n">
+        <v>2</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="B517" t="n">
+        <v>101007</v>
+      </c>
+      <c r="C517" t="n">
+        <v>3</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="B518" t="n">
+        <v>101007</v>
+      </c>
+      <c r="C518" t="n">
+        <v>4</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="B519" t="n">
+        <v>101007</v>
+      </c>
+      <c r="C519" t="n">
+        <v>5</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="B520" t="n">
+        <v>101008</v>
+      </c>
+      <c r="C520" t="n">
+        <v>1</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="B521" t="n">
+        <v>101009</v>
+      </c>
+      <c r="C521" t="n">
+        <v>1</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="B522" t="n">
+        <v>101010</v>
+      </c>
+      <c r="C522" t="n">
+        <v>1</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="B523" t="n">
+        <v>101011</v>
+      </c>
+      <c r="C523" t="n">
+        <v>1</v>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="B524" t="n">
+        <v>101012</v>
+      </c>
+      <c r="C524" t="n">
+        <v>1</v>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="B525" t="n">
+        <v>101013</v>
+      </c>
+      <c r="C525" t="n">
+        <v>1</v>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="B526" t="n">
+        <v>101014</v>
+      </c>
+      <c r="C526" t="n">
+        <v>1</v>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="B527" t="n">
+        <v>101015</v>
+      </c>
+      <c r="C527" t="n">
+        <v>1</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="B528" t="n">
+        <v>101015</v>
+      </c>
+      <c r="C528" t="n">
+        <v>2</v>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="B529" t="n">
+        <v>101016</v>
+      </c>
+      <c r="C529" t="n">
+        <v>1</v>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="B530" t="n">
+        <v>101017</v>
+      </c>
+      <c r="C530" t="n">
+        <v>1</v>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="B531" t="n">
+        <v>101018</v>
+      </c>
+      <c r="C531" t="n">
+        <v>1</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K531" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="B532" t="n">
+        <v>101019</v>
+      </c>
+      <c r="C532" t="n">
+        <v>1</v>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="B533" t="n">
+        <v>101020</v>
+      </c>
+      <c r="C533" t="n">
+        <v>1</v>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="B534" t="n">
+        <v>101021</v>
+      </c>
+      <c r="C534" t="n">
+        <v>1</v>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="B535" t="n">
+        <v>101022</v>
+      </c>
+      <c r="C535" t="n">
+        <v>1</v>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="B536" t="n">
+        <v>101022</v>
+      </c>
+      <c r="C536" t="n">
+        <v>2</v>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="B537" t="n">
+        <v>101023</v>
+      </c>
+      <c r="C537" t="n">
+        <v>1</v>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="B538" t="n">
+        <v>101024</v>
+      </c>
+      <c r="C538" t="n">
+        <v>1</v>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="B539" t="n">
+        <v>101025</v>
+      </c>
+      <c r="C539" t="n">
+        <v>1</v>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="B540" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C540" t="n">
+        <v>1</v>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="B541" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C541" t="n">
+        <v>10</v>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="B542" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C542" t="n">
+        <v>11</v>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="B543" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C543" t="n">
+        <v>12</v>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="B544" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C544" t="n">
+        <v>13</v>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="B545" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C545" t="n">
+        <v>14</v>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="B546" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C546" t="n">
+        <v>15</v>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="B547" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C547" t="n">
+        <v>16</v>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="B548" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C548" t="n">
+        <v>17</v>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="B549" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C549" t="n">
+        <v>18</v>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="B550" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C550" t="n">
+        <v>19</v>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="B551" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C551" t="n">
+        <v>2</v>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="B552" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C552" t="n">
+        <v>20</v>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="B553" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C553" t="n">
+        <v>21</v>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>0.04762</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>0.04762</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="B554" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C554" t="n">
+        <v>3</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="B555" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C555" t="n">
+        <v>4</v>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="B556" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C556" t="n">
+        <v>5</v>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="B557" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C557" t="n">
+        <v>6</v>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="B558" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C558" t="n">
+        <v>7</v>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="B559" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C559" t="n">
+        <v>8</v>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="B560" t="n">
+        <v>101026</v>
+      </c>
+      <c r="C560" t="n">
+        <v>9</v>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>0.047619</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>

--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K560"/>
+  <dimension ref="A1:K609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -24548,6 +24548,2068 @@
       <c r="J560" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="B561" t="n">
+        <v>111001</v>
+      </c>
+      <c r="C561" t="n">
+        <v>1</v>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="B562" t="n">
+        <v>111002</v>
+      </c>
+      <c r="C562" t="n">
+        <v>1</v>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="B563" t="n">
+        <v>111003</v>
+      </c>
+      <c r="C563" t="n">
+        <v>1</v>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="B564" t="n">
+        <v>111004</v>
+      </c>
+      <c r="C564" t="n">
+        <v>1</v>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="B565" t="n">
+        <v>111005</v>
+      </c>
+      <c r="C565" t="n">
+        <v>1</v>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="B566" t="n">
+        <v>111006</v>
+      </c>
+      <c r="C566" t="n">
+        <v>1</v>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="B567" t="n">
+        <v>111007</v>
+      </c>
+      <c r="C567" t="n">
+        <v>1</v>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="B568" t="n">
+        <v>111007</v>
+      </c>
+      <c r="C568" t="n">
+        <v>2</v>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="B569" t="n">
+        <v>111008</v>
+      </c>
+      <c r="C569" t="n">
+        <v>1</v>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="B570" t="n">
+        <v>111009</v>
+      </c>
+      <c r="C570" t="n">
+        <v>1</v>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="B571" t="n">
+        <v>111009</v>
+      </c>
+      <c r="C571" t="n">
+        <v>2</v>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="B572" t="n">
+        <v>111009</v>
+      </c>
+      <c r="C572" t="n">
+        <v>3</v>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="B573" t="n">
+        <v>111009</v>
+      </c>
+      <c r="C573" t="n">
+        <v>4</v>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="B574" t="n">
+        <v>111009</v>
+      </c>
+      <c r="C574" t="n">
+        <v>5</v>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="B575" t="n">
+        <v>111010</v>
+      </c>
+      <c r="C575" t="n">
+        <v>1</v>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="B576" t="n">
+        <v>111010</v>
+      </c>
+      <c r="C576" t="n">
+        <v>2</v>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="B577" t="n">
+        <v>111010</v>
+      </c>
+      <c r="C577" t="n">
+        <v>3</v>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="B578" t="n">
+        <v>111010</v>
+      </c>
+      <c r="C578" t="n">
+        <v>4</v>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="B579" t="n">
+        <v>111010</v>
+      </c>
+      <c r="C579" t="n">
+        <v>5</v>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="B580" t="n">
+        <v>111011</v>
+      </c>
+      <c r="C580" t="n">
+        <v>1</v>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="B581" t="n">
+        <v>111012</v>
+      </c>
+      <c r="C581" t="n">
+        <v>1</v>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="B582" t="n">
+        <v>111012</v>
+      </c>
+      <c r="C582" t="n">
+        <v>2</v>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="B583" t="n">
+        <v>111012</v>
+      </c>
+      <c r="C583" t="n">
+        <v>3</v>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="B584" t="n">
+        <v>111012</v>
+      </c>
+      <c r="C584" t="n">
+        <v>4</v>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="B585" t="n">
+        <v>111012</v>
+      </c>
+      <c r="C585" t="n">
+        <v>5</v>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="B586" t="n">
+        <v>111012</v>
+      </c>
+      <c r="C586" t="n">
+        <v>6</v>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>0.16667</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>0.16667</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="B587" t="n">
+        <v>111013</v>
+      </c>
+      <c r="C587" t="n">
+        <v>1</v>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="B588" t="n">
+        <v>111014</v>
+      </c>
+      <c r="C588" t="n">
+        <v>1</v>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="B589" t="n">
+        <v>111015</v>
+      </c>
+      <c r="C589" t="n">
+        <v>1</v>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="B590" t="n">
+        <v>111016</v>
+      </c>
+      <c r="C590" t="n">
+        <v>1</v>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="B591" t="n">
+        <v>111017</v>
+      </c>
+      <c r="C591" t="n">
+        <v>1</v>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="B592" t="n">
+        <v>111018</v>
+      </c>
+      <c r="C592" t="n">
+        <v>1</v>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="B593" t="n">
+        <v>111019</v>
+      </c>
+      <c r="C593" t="n">
+        <v>1</v>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="B594" t="n">
+        <v>111020</v>
+      </c>
+      <c r="C594" t="n">
+        <v>1</v>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="B595" t="n">
+        <v>111020</v>
+      </c>
+      <c r="C595" t="n">
+        <v>2</v>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="B596" t="n">
+        <v>111021</v>
+      </c>
+      <c r="C596" t="n">
+        <v>1</v>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="B597" t="n">
+        <v>111022</v>
+      </c>
+      <c r="C597" t="n">
+        <v>1</v>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="B598" t="n">
+        <v>111022</v>
+      </c>
+      <c r="C598" t="n">
+        <v>2</v>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="B599" t="n">
+        <v>111023</v>
+      </c>
+      <c r="C599" t="n">
+        <v>1</v>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="B600" t="n">
+        <v>111023</v>
+      </c>
+      <c r="C600" t="n">
+        <v>2</v>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="B601" t="n">
+        <v>111023</v>
+      </c>
+      <c r="C601" t="n">
+        <v>3</v>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="B602" t="n">
+        <v>111023</v>
+      </c>
+      <c r="C602" t="n">
+        <v>4</v>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="B603" t="n">
+        <v>111023</v>
+      </c>
+      <c r="C603" t="n">
+        <v>5</v>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="B604" t="n">
+        <v>111023</v>
+      </c>
+      <c r="C604" t="n">
+        <v>6</v>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="B605" t="n">
+        <v>111023</v>
+      </c>
+      <c r="C605" t="n">
+        <v>7</v>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="B606" t="n">
+        <v>111023</v>
+      </c>
+      <c r="C606" t="n">
+        <v>8</v>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>0.111111</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="B607" t="n">
+        <v>111023</v>
+      </c>
+      <c r="C607" t="n">
+        <v>9</v>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>0.111112</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>0.111112</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="B608" t="n">
+        <v>111024</v>
+      </c>
+      <c r="C608" t="n">
+        <v>1</v>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="B609" t="n">
+        <v>111025</v>
+      </c>
+      <c r="C609" t="n">
+        <v>1</v>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>

--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K609"/>
+  <dimension ref="A1:K653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -26610,6 +26610,1886 @@
       <c r="J609" t="inlineStr">
         <is>
           <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="B610" t="n">
+        <v>121001</v>
+      </c>
+      <c r="C610" t="n">
+        <v>1</v>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="B611" t="n">
+        <v>121001</v>
+      </c>
+      <c r="C611" t="n">
+        <v>2</v>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="B612" t="n">
+        <v>121001</v>
+      </c>
+      <c r="C612" t="n">
+        <v>3</v>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="B613" t="n">
+        <v>121001</v>
+      </c>
+      <c r="C613" t="n">
+        <v>4</v>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="B614" t="n">
+        <v>121001</v>
+      </c>
+      <c r="C614" t="n">
+        <v>5</v>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="B615" t="n">
+        <v>121002</v>
+      </c>
+      <c r="C615" t="n">
+        <v>1</v>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="B616" t="n">
+        <v>121003</v>
+      </c>
+      <c r="C616" t="n">
+        <v>1</v>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="B617" t="n">
+        <v>121004</v>
+      </c>
+      <c r="C617" t="n">
+        <v>1</v>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="B618" t="n">
+        <v>121005</v>
+      </c>
+      <c r="C618" t="n">
+        <v>1</v>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="B619" t="n">
+        <v>121006</v>
+      </c>
+      <c r="C619" t="n">
+        <v>1</v>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="B620" t="n">
+        <v>121007</v>
+      </c>
+      <c r="C620" t="n">
+        <v>1</v>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="B621" t="n">
+        <v>121008</v>
+      </c>
+      <c r="C621" t="n">
+        <v>1</v>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="B622" t="n">
+        <v>121008</v>
+      </c>
+      <c r="C622" t="n">
+        <v>2</v>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="B623" t="n">
+        <v>121009</v>
+      </c>
+      <c r="C623" t="n">
+        <v>1</v>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="B624" t="n">
+        <v>121010</v>
+      </c>
+      <c r="C624" t="n">
+        <v>1</v>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="B625" t="n">
+        <v>121011</v>
+      </c>
+      <c r="C625" t="n">
+        <v>1</v>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="B626" t="n">
+        <v>121011</v>
+      </c>
+      <c r="C626" t="n">
+        <v>2</v>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="B627" t="n">
+        <v>121012</v>
+      </c>
+      <c r="C627" t="n">
+        <v>1</v>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="B628" t="n">
+        <v>121012</v>
+      </c>
+      <c r="C628" t="n">
+        <v>2</v>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="B629" t="n">
+        <v>121012</v>
+      </c>
+      <c r="C629" t="n">
+        <v>3</v>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="B630" t="n">
+        <v>121013</v>
+      </c>
+      <c r="C630" t="n">
+        <v>1</v>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="B631" t="n">
+        <v>121014</v>
+      </c>
+      <c r="C631" t="n">
+        <v>1</v>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="B632" t="n">
+        <v>121015</v>
+      </c>
+      <c r="C632" t="n">
+        <v>1</v>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="B633" t="n">
+        <v>121016</v>
+      </c>
+      <c r="C633" t="n">
+        <v>1</v>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K633" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="B634" t="n">
+        <v>121017</v>
+      </c>
+      <c r="C634" t="n">
+        <v>1</v>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="B635" t="n">
+        <v>121017</v>
+      </c>
+      <c r="C635" t="n">
+        <v>2</v>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="B636" t="n">
+        <v>121018</v>
+      </c>
+      <c r="C636" t="n">
+        <v>1</v>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="B637" t="n">
+        <v>121018</v>
+      </c>
+      <c r="C637" t="n">
+        <v>2</v>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>0.333333</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="B638" t="n">
+        <v>121018</v>
+      </c>
+      <c r="C638" t="n">
+        <v>3</v>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>0.333334</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="B639" t="n">
+        <v>121019</v>
+      </c>
+      <c r="C639" t="n">
+        <v>1</v>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="B640" t="n">
+        <v>121020</v>
+      </c>
+      <c r="C640" t="n">
+        <v>1</v>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="B641" t="n">
+        <v>121021</v>
+      </c>
+      <c r="C641" t="n">
+        <v>1</v>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>parameter.03</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="B642" t="n">
+        <v>121022</v>
+      </c>
+      <c r="C642" t="n">
+        <v>1</v>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="B643" t="n">
+        <v>121023</v>
+      </c>
+      <c r="C643" t="n">
+        <v>1</v>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="B644" t="n">
+        <v>121024</v>
+      </c>
+      <c r="C644" t="n">
+        <v>1</v>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>parameter.04</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="B645" t="n">
+        <v>121025</v>
+      </c>
+      <c r="C645" t="n">
+        <v>1</v>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="B646" t="n">
+        <v>121026</v>
+      </c>
+      <c r="C646" t="n">
+        <v>1</v>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="B647" t="n">
+        <v>121026</v>
+      </c>
+      <c r="C647" t="n">
+        <v>2</v>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>parameter.06</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="B648" t="n">
+        <v>121026</v>
+      </c>
+      <c r="C648" t="n">
+        <v>3</v>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>parameter.06</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="B649" t="n">
+        <v>121026</v>
+      </c>
+      <c r="C649" t="n">
+        <v>4</v>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>parameter.06</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="B650" t="n">
+        <v>121026</v>
+      </c>
+      <c r="C650" t="n">
+        <v>5</v>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>0.166666</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>parameter.06</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="B651" t="n">
+        <v>121026</v>
+      </c>
+      <c r="C651" t="n">
+        <v>6</v>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>BounceDraw</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>0.16667</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>0.16667</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>parameter.06</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="B652" t="n">
+        <v>121027</v>
+      </c>
+      <c r="C652" t="n">
+        <v>1</v>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="B653" t="n">
+        <v>121027</v>
+      </c>
+      <c r="C653" t="n">
+        <v>2</v>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>

--- a/config/data/HitPlanHit.xlsx
+++ b/config/data/HitPlanHit.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K653"/>
+  <dimension ref="A1:K661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -28490,6 +28490,345 @@
       <c r="J653" t="inlineStr">
         <is>
           <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="B654" t="n">
+        <v>131001</v>
+      </c>
+      <c r="C654" t="n">
+        <v>1</v>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="B655" t="n">
+        <v>131002</v>
+      </c>
+      <c r="C655" t="n">
+        <v>1</v>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="B656" t="n">
+        <v>131003</v>
+      </c>
+      <c r="C656" t="n">
+        <v>1</v>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="B657" t="n">
+        <v>131004</v>
+      </c>
+      <c r="C657" t="n">
+        <v>1</v>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="B658" t="n">
+        <v>131004</v>
+      </c>
+      <c r="C658" t="n">
+        <v>2</v>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="B659" t="n">
+        <v>131005</v>
+      </c>
+      <c r="C659" t="n">
+        <v>1</v>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="B660" t="n">
+        <v>131005</v>
+      </c>
+      <c r="C660" t="n">
+        <v>2</v>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>parameter.02</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="B661" t="n">
+        <v>131006</v>
+      </c>
+      <c r="C661" t="n">
+        <v>1</v>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>PerTarget</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>parameter.01</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>
